--- a/data.xlsx
+++ b/data.xlsx
@@ -661,7 +661,11 @@
           <t>GitHub repository link</t>
         </is>
       </c>
-      <c r="C7" s="7" t="n"/>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>https://github.com/Astitvaaaaaaaaaaa-hub/consent-privacy-judgments</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="B8" s="6" t="inlineStr">
@@ -695,7 +699,7 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Sahil Islam, Division C</t>
+          <t>Sahil Islam, Division D</t>
         </is>
       </c>
     </row>
@@ -707,7 +711,7 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>Khushi Gurm, Division C</t>
+          <t>Khushi Gurm, Division B</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -723,7 +723,7 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>22-10-2026</t>
+          <t>26-10-2026</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>W.P. (Crl.) No. 314 of 2021</t>
+          <t>2021 INSC 682 (W.P. (Crl.) No. 314 of 2021)</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="K6" s="12" t="inlineStr">
         <is>
-          <t>Art 21</t>
+          <t>Art 21 (paras 32–36, 49–50, 55–64)</t>
         </is>
       </c>
       <c r="L6" s="12" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="K7" s="12" t="inlineStr">
         <is>
-          <t>r 3B MTP Rules; s 3(2) MTP Act</t>
+          <t>r 3B MTP Rules; s 3(2) MTP Act; s 19(1) POCSO; Art 21 (paras 81, 89–93, 96–108)</t>
         </is>
       </c>
       <c r="L7" s="12" t="inlineStr">
@@ -1090,33 +1090,33 @@
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>Aparna Ajinkya Firodia v. Ajinkya Arun Firodia</t>
+          <t>Common Cause (A Registered Society) v. Union of India</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>2023 INSC 146</t>
+          <t>2023 INSC 77 (M.A. No. 1699 of 2019 in W.P. (C) No. 215 of 2005)</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>20-02-2023</t>
+          <t>24-01-2023</t>
         </is>
       </c>
       <c r="E8" s="12" t="n">
         <v>2023</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
-          <t>Civil appeal</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
-          <t>Individual</t>
+          <t>Association or NGO</t>
         </is>
       </c>
       <c r="I8" s="12" t="inlineStr">
@@ -1126,37 +1126,37 @@
       </c>
       <c r="J8" s="12" t="inlineStr">
         <is>
-          <t>Individual</t>
+          <t>Association or NGO</t>
         </is>
       </c>
       <c r="K8" s="12" t="inlineStr">
         <is>
-          <t>s 112 Evidence Act; Art 21</t>
+          <t>Art 21 (paras 4–5, 8–9, 12)</t>
         </is>
       </c>
       <c r="L8" s="12" t="inlineStr">
         <is>
-          <t>Whether a family court can order a DNA test of a child to prove the wife's adultery.</t>
+          <t>Whether the 2018 guidelines on living wills and withdrawal of life support, challenged as unworkable by the Indian Society of Critical Care Medicine, should be simplified.</t>
         </is>
       </c>
       <c r="M8" s="12" t="inlineStr">
         <is>
-          <t>DNA tests of children cannot be ordered routinely; the child's privacy and legitimacy must be protected, so the order was set aside.</t>
+          <t>The Court eased the procedure: attestation by a notary or gazetted officer instead of a magistrate, and primary and secondary medical boards with fixed timelines, so that advance directives can work in practice.</t>
         </is>
       </c>
       <c r="N8" s="12" t="inlineStr">
         <is>
-          <t>Goutam Kundu v. State of West Bengal (1993)</t>
+          <t>Common Cause v. Union of India (2018)</t>
         </is>
       </c>
       <c r="O8" s="12" t="inlineStr">
         <is>
-          <t>https://api.sci.gov.in/supremecourt/2022/9691/9691_2022_15_1501_42221_Judgement_20-Feb-2023.pdf</t>
+          <t>https://digiscr.sci.gov.in/view_judgment?id=MzM3MTg%3D</t>
         </is>
       </c>
       <c r="P8" s="12" t="inlineStr">
         <is>
-          <t>Sahil Islam</t>
+          <t>Astitva Agrawal</t>
         </is>
       </c>
     </row>
@@ -1166,33 +1166,33 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Association for Democratic Reforms v. Union of India</t>
+          <t>Aparna Ajinkya Firodia v. Ajinkya Arun Firodia</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>2024 INSC 113</t>
+          <t>2023 INSC 146 (arising out of SLP (C) No. 9855 of 2022)</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>15-02-2024</t>
+          <t>20-02-2023</t>
         </is>
       </c>
       <c r="E9" s="12" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="F9" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
-          <t>Writ petition</t>
+          <t>Civil appeal</t>
         </is>
       </c>
       <c r="H9" s="12" t="inlineStr">
         <is>
-          <t>Association or NGO</t>
+          <t>Individual</t>
         </is>
       </c>
       <c r="I9" s="12" t="inlineStr">
@@ -1202,37 +1202,37 @@
       </c>
       <c r="J9" s="12" t="inlineStr">
         <is>
-          <t>Association or NGO</t>
+          <t>Individual</t>
         </is>
       </c>
       <c r="K9" s="12" t="inlineStr">
         <is>
-          <t>Art 19(1)(a); Art 21</t>
+          <t>s 112 Evidence Act; Art 21 (Nagarathna J., paras 11.1–12, 16–24, 27)</t>
         </is>
       </c>
       <c r="L9" s="12" t="inlineStr">
         <is>
-          <t>Whether donor informational privacy justifies anonymous political funding through electoral bonds.</t>
+          <t>Whether a family court can order a DNA test of a child to prove the wife's adultery.</t>
         </is>
       </c>
       <c r="M9" s="12" t="inlineStr">
         <is>
-          <t>Voters' right to information outweighed donor privacy; the Electoral Bond Scheme was struck down.</t>
+          <t>DNA tests of children cannot be ordered routinely; the child's privacy and legitimacy must be protected, so the order was set aside.</t>
         </is>
       </c>
       <c r="N9" s="12" t="inlineStr">
         <is>
-          <t>K.S. Puttaswamy v. Union of India (2017)</t>
+          <t>Goutam Kundu v. State of West Bengal (1993)</t>
         </is>
       </c>
       <c r="O9" s="12" t="inlineStr">
         <is>
-          <t>https://api.sci.gov.in/supremecourt/2017/27935/27935_2017_1_1501_50573_Judgement_15-Feb-2024.pdf</t>
+          <t>https://api.sci.gov.in/supremecourt/2022/9691/9691_2022_15_1501_42221_Judgement_20-Feb-2023.pdf</t>
         </is>
       </c>
       <c r="P9" s="12" t="inlineStr">
         <is>
-          <t>Astitva Agrawal</t>
+          <t>Sahil Islam</t>
         </is>
       </c>
     </row>
@@ -1242,33 +1242,33 @@
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>Frank Vitus v. Narcotics Control Bureau</t>
+          <t>Association for Democratic Reforms v. Union of India</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>2024 INSC 479</t>
+          <t>2024 INSC 113</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>08-07-2024</t>
+          <t>15-02-2024</t>
         </is>
       </c>
       <c r="E10" s="12" t="n">
         <v>2024</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
-          <t>Criminal appeal</t>
+          <t>Writ petition</t>
         </is>
       </c>
       <c r="H10" s="12" t="inlineStr">
         <is>
-          <t>Individual</t>
+          <t>Association or NGO</t>
         </is>
       </c>
       <c r="I10" s="12" t="inlineStr">
@@ -1278,37 +1278,37 @@
       </c>
       <c r="J10" s="12" t="inlineStr">
         <is>
-          <t>Individual</t>
+          <t>Association or NGO</t>
         </is>
       </c>
       <c r="K10" s="12" t="inlineStr">
         <is>
-          <t>Art 21</t>
+          <t>Art 19(1)(a); Art 21 (CJI's opinion, paras 102–104, 160–174, 216–219)</t>
         </is>
       </c>
       <c r="L10" s="12" t="inlineStr">
         <is>
-          <t>Whether bail can require the accused to share a Google Maps PIN location with the police.</t>
+          <t>Whether donor informational privacy justifies anonymous political funding through electoral bonds.</t>
         </is>
       </c>
       <c r="M10" s="12" t="inlineStr">
         <is>
-          <t>A bail condition letting police track every movement of the accused violates privacy; the PIN condition was deleted.</t>
+          <t>Voters' right to information outweighed donor privacy; the Electoral Bond Scheme was struck down.</t>
         </is>
       </c>
       <c r="N10" s="12" t="inlineStr">
         <is>
-          <t>State of A.P. v. Challa Ramkrishna Reddy (2000)</t>
+          <t>PUCL v. Union of India (2003)</t>
         </is>
       </c>
       <c r="O10" s="12" t="inlineStr">
         <is>
-          <t>https://webapi.sci.gov.in/supremecourt/2023/6687/6687_2023_6_1509_53522_Judgement_08-Jul-2024.pdf</t>
+          <t>https://api.sci.gov.in/supremecourt/2017/27935/27935_2017_1_1501_50573_Judgement_15-Feb-2024.pdf</t>
         </is>
       </c>
       <c r="P10" s="12" t="inlineStr">
         <is>
-          <t>Anmol Kumar Sinha</t>
+          <t>Astitva Agrawal</t>
         </is>
       </c>
     </row>
@@ -1318,17 +1318,17 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>In Re: Right to Privacy of Adolescents (with State of West Bengal v. Probhat Purkait)</t>
+          <t>Frank Vitus v. Narcotics Control Bureau</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>2024 INSC 614</t>
+          <t>2024 INSC 479 (arising out of SLP (Crl.) Nos. 6339–6340 of 2023)</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>20-08-2024</t>
+          <t>08-07-2024</t>
         </is>
       </c>
       <c r="E11" s="12" t="n">
@@ -1339,52 +1339,52 @@
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
+          <t>Criminal appeal</t>
+        </is>
+      </c>
+      <c r="H11" s="12" t="inlineStr">
+        <is>
+          <t>Individual</t>
+        </is>
+      </c>
+      <c r="I11" s="12" t="inlineStr">
+        <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="H11" s="12" t="inlineStr">
-        <is>
-          <t>State or public body</t>
-        </is>
-      </c>
-      <c r="I11" s="12" t="inlineStr">
-        <is>
-          <t>Partly allowed</t>
-        </is>
-      </c>
       <c r="J11" s="12" t="inlineStr">
         <is>
-          <t>State or public body</t>
+          <t>Individual</t>
         </is>
       </c>
       <c r="K11" s="12" t="inlineStr">
         <is>
-          <t>s 6 POCSO; s 19(6) POCSO</t>
+          <t>Art 21 (paras 10–10.2, 15)</t>
         </is>
       </c>
       <c r="L11" s="12" t="inlineStr">
         <is>
-          <t>Whether a High Court could acquit a POCSO accused on the footing of a ‘consensual’ adolescent relationship and lecture adolescents on sexual conduct.</t>
+          <t>Whether bail can require the accused to share a Google Maps PIN location with the police.</t>
         </is>
       </c>
       <c r="M11" s="12" t="inlineStr">
         <is>
-          <t>The conviction was restored and the High Court's remarks set aside; a minor's consent is immaterial under POCSO.</t>
+          <t>A bail condition letting police track every movement of the accused would violate privacy under Article 21; the Google Maps PIN condition and the embassy-certificate condition were deleted, with final orders left for a later date.</t>
         </is>
       </c>
       <c r="N11" s="12" t="inlineStr">
         <is>
-          <t>Gian Singh v. State of Punjab (2012)</t>
+          <t>State of A.P. v. Challa Ramkrishna Reddy (2000)</t>
         </is>
       </c>
       <c r="O11" s="12" t="inlineStr">
         <is>
-          <t>https://api.sci.gov.in/supremecourt/2023/51208/51208_2023_6_1501_54805_Judgement_20-Aug-2024.pdf</t>
+          <t>https://api.sci.gov.in/supremecourt/2023/6687/6687_2023_6_1509_53522_Judgement_08-Jul-2024.pdf</t>
         </is>
       </c>
       <c r="P11" s="12" t="inlineStr">
         <is>
-          <t>Khushi Gurm</t>
+          <t>Anmol Kumar Sinha</t>
         </is>
       </c>
     </row>
@@ -1394,73 +1394,73 @@
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>Amlesh Kumar v. State of Bihar</t>
+          <t>In Re: Right to Privacy of Adolescents (with State of West Bengal v. Probhat Purkait)</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>2025 INSC 810</t>
+          <t>2024 INSC 614 (Suo Motu W.P. (C) No. 3 of 2023 with Crl. A. No. 1451 of 2024)</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>09-06-2025</t>
+          <t>20-08-2024</t>
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="F12" s="12" t="n">
         <v>2</v>
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
-          <t>Criminal appeal</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="H12" s="12" t="inlineStr">
         <is>
-          <t>Individual</t>
+          <t>State or public body</t>
         </is>
       </c>
       <c r="I12" s="12" t="inlineStr">
         <is>
-          <t>Allowed</t>
+          <t>Partly allowed</t>
         </is>
       </c>
       <c r="J12" s="12" t="inlineStr">
         <is>
-          <t>Individual</t>
+          <t>State or public body</t>
         </is>
       </c>
       <c r="K12" s="12" t="inlineStr">
         <is>
-          <t>Art 20(3); Art 21</t>
+          <t>s 6 POCSO; s 19(6) POCSO (paras 11, 19–21, 35–37, 44)</t>
         </is>
       </c>
       <c r="L12" s="12" t="inlineStr">
         <is>
-          <t>Whether a High Court could accept a police plan to narco-test all accused while hearing a bail plea.</t>
+          <t>Whether a High Court could acquit a POCSO accused on the footing of a ‘consensual’ adolescent relationship and lecture adolescents on sexual conduct.</t>
         </is>
       </c>
       <c r="M12" s="12" t="inlineStr">
         <is>
-          <t>Forced narco tests are never permissible; a voluntary test may be sought only at the defence stage with court permission.</t>
+          <t>The conviction was restored and the High Court's remarks set aside; a minor's consent is immaterial under POCSO.</t>
         </is>
       </c>
       <c r="N12" s="12" t="inlineStr">
         <is>
-          <t>Selvi v. State of Karnataka (2010)</t>
+          <t>Gian Singh v. State of Punjab (2012)</t>
         </is>
       </c>
       <c r="O12" s="12" t="inlineStr">
         <is>
-          <t>https://api.sci.gov.in/supremecourt/2024/9701/9701_2024_4_1501_62184_Judgement_09-Jun-2025.pdf</t>
+          <t>https://api.sci.gov.in/supremecourt/2023/51208/51208_2023_6_1501_54805_Judgement_20-Aug-2024.pdf</t>
         </is>
       </c>
       <c r="P12" s="12" t="inlineStr">
         <is>
-          <t>Sahil Islam</t>
+          <t>Khushi Gurm</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Vibhor Garg v. Neha</t>
+          <t>Ivan Rathinam v. Milan Joseph</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>2025 INSC 829</t>
+          <t>2025 INSC 115 (Crl. A. No. 413 of 2025)</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>14-07-2025</t>
+          <t>28-01-2025</t>
         </is>
       </c>
       <c r="E13" s="12" t="n">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
-          <t>Civil appeal</t>
+          <t>Criminal appeal</t>
         </is>
       </c>
       <c r="H13" s="12" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="K13" s="12" t="inlineStr">
         <is>
-          <t>s 122 Evidence Act; Art 21</t>
+          <t>s 112 Evidence Act; Art 21 (paras 35–47, 52, 70–71)</t>
         </is>
       </c>
       <c r="L13" s="12" t="inlineStr">
         <is>
-          <t>Whether phone calls secretly recorded by one spouse are admissible in divorce proceedings.</t>
+          <t>Whether a man alleged to be a child's biological father could be compelled to take a DNA test in maintenance proceedings, when the mother was married to another man at the time of birth.</t>
         </is>
       </c>
       <c r="M13" s="12" t="inlineStr">
         <is>
-          <t>Such recordings are admissible; the wife's privacy objection did not bar them, and the Family Court's order was restored.</t>
+          <t>A DNA test needs an 'eminent need': existing evidence must be insufficient and the balance of interests must favour the test. Neither was met, so the direction was set aside and the respondent was presumed legitimate.</t>
         </is>
       </c>
       <c r="N13" s="12" t="inlineStr">
         <is>
-          <t>R.M. Malkani v. State of Maharashtra (1973)</t>
+          <t>Goutam Kundu v. State of West Bengal (1993)</t>
         </is>
       </c>
       <c r="O13" s="12" t="inlineStr">
         <is>
-          <t>https://api.sci.gov.in/supremecourt/2021/31421/31421_2021_5_1501_62289_Judgement_14-Jul-2025.pdf</t>
+          <t>https://api.sci.gov.in/supremecourt/2018/20907/20907_2018_3_1501_58757_Judgement_28-Jan-2025.pdf</t>
         </is>
       </c>
       <c r="P13" s="12" t="inlineStr">
         <is>
-          <t>Khushi Gurm</t>
+          <t>Sahil Islam</t>
         </is>
       </c>
     </row>
@@ -1546,17 +1546,17 @@
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>R. Rajendran v. Kamar Nisha</t>
+          <t>Amlesh Kumar v. State of Bihar</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>2025 INSC 1304 (Criminal Appeal No. 1013 of 2021)</t>
+          <t>2025 INSC 810 (arising out of SLP (Crl.) No. 5392 of 2024)</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>10-11-2025</t>
+          <t>09-06-2025</t>
         </is>
       </c>
       <c r="E14" s="12" t="n">
@@ -1587,32 +1587,32 @@
       </c>
       <c r="K14" s="12" t="inlineStr">
         <is>
-          <t>Art 21; s 112 Evidence Act; ss 53, 53A CrPC</t>
+          <t>Art 20(3); Art 21 (paras 8–10, 16, 20–21, 23)</t>
         </is>
       </c>
       <c r="L14" s="12" t="inlineStr">
         <is>
-          <t>Whether a man accused of cheating could be forced to give a DNA sample to establish a child's paternity.</t>
+          <t>Whether a High Court could accept a police plan to narco-test all accused while hearing a bail plea.</t>
         </is>
       </c>
       <c r="M14" s="12" t="inlineStr">
         <is>
-          <t>Forced DNA testing is a grave intrusion on privacy and must be lawful, necessary and proportionate, with a nexus to the offence. Paternity was collateral to the charges, so the direction was set aside.</t>
+          <t>Forced narco tests are never permissible; a voluntary test may be sought only at the defence stage with court permission.</t>
         </is>
       </c>
       <c r="N14" s="12" t="inlineStr">
         <is>
-          <t>Goutam Kundu v. State of West Bengal (1993)</t>
+          <t>Selvi v. State of Karnataka (2010)</t>
         </is>
       </c>
       <c r="O14" s="12" t="inlineStr">
         <is>
-          <t>https://api.sci.gov.in/supremecourt/2017/16058/16058_2017_14_1501_65616_Judgement_10-Nov-2025.pdf</t>
+          <t>https://api.sci.gov.in/supremecourt/2024/9701/9701_2024_4_1501_62184_Judgement_09-Jun-2025.pdf</t>
         </is>
       </c>
       <c r="P14" s="12" t="inlineStr">
         <is>
-          <t>Khushi Gurm</t>
+          <t>Sahil Islam</t>
         </is>
       </c>
     </row>
@@ -1622,28 +1622,28 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Harish Rana v. Union of India</t>
+          <t>Vibhor Garg v. Neha</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>2026 INSC 222</t>
+          <t>2025 INSC 829 (arising out of SLP (C) No. 21195 of 2021)</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>11-03-2026</t>
+          <t>14-07-2025</t>
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="F15" s="12" t="n">
         <v>2</v>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Civil appeal</t>
         </is>
       </c>
       <c r="H15" s="12" t="inlineStr">
@@ -1663,32 +1663,32 @@
       </c>
       <c r="K15" s="12" t="inlineStr">
         <is>
-          <t>Art 21</t>
+          <t>s 122 Evidence Act; Art 21 (paras 10–10.3, 12–12.6, 13)</t>
         </is>
       </c>
       <c r="L15" s="12" t="inlineStr">
         <is>
-          <t>How passive euthanasia applies to a patient in a permanent vegetative state who cannot consent and left no advance directive.</t>
+          <t>Whether phone calls secretly recorded by one spouse are admissible in divorce proceedings.</t>
         </is>
       </c>
       <c r="M15" s="12" t="inlineStr">
         <is>
-          <t>Withdrawal of artificial nutrition was permitted through surrogate decision-making and medical boards.</t>
+          <t>Such recordings are admissible; the wife's privacy objection did not bar them, and the Family Court's order was restored.</t>
         </is>
       </c>
       <c r="N15" s="12" t="inlineStr">
         <is>
-          <t>Common Cause v. Union of India (2018)</t>
+          <t>M.C. Verghese v. T.J. Ponnan (1969)</t>
         </is>
       </c>
       <c r="O15" s="12" t="inlineStr">
         <is>
-          <t>https://api.sci.gov.in/supremecourt/2025/60980/60980_2025_7_1501_69246_Judgement_11-Mar-2026.pdf</t>
+          <t>https://api.sci.gov.in/supremecourt/2021/31421/31421_2021_5_1501_62289_Judgement_14-Jul-2025.pdf</t>
         </is>
       </c>
       <c r="P15" s="12" t="inlineStr">
         <is>
-          <t>Astitva Agrawal</t>
+          <t>Khushi Gurm</t>
         </is>
       </c>
     </row>
@@ -1698,28 +1698,28 @@
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>Chaturbhuj Pradhan v. Amar Pradhan</t>
+          <t>R. Rajendran v. Kamar Nisha</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>2026 INSC 600 (arising out of SLP (C) No. 4016 of 2026)</t>
+          <t>2025 INSC 1304 (Criminal Appeal No. 1013 of 2021)</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>29-05-2026</t>
+          <t>10-11-2025</t>
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="F16" s="12" t="n">
         <v>2</v>
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
-          <t>Civil appeal</t>
+          <t>Criminal appeal</t>
         </is>
       </c>
       <c r="H16" s="12" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="I16" s="12" t="inlineStr">
         <is>
-          <t>Dismissed</t>
+          <t>Allowed</t>
         </is>
       </c>
       <c r="J16" s="12" t="inlineStr">
@@ -1739,32 +1739,32 @@
       </c>
       <c r="K16" s="12" t="inlineStr">
         <is>
-          <t>s 112 Evidence Act; Art 21</t>
+          <t>Art 21; s 112 Evidence Act; ss 53, 53A CrPC (paras 37, 45–48, 52–54, 58–61)</t>
         </is>
       </c>
       <c r="L16" s="12" t="inlineStr">
         <is>
-          <t>Whether a man could be compelled to take a DNA test in a suit where the plaintiff claims to be his son.</t>
+          <t>Whether a man accused of cheating could be forced to give a DNA sample to establish a child's paternity.</t>
         </is>
       </c>
       <c r="M16" s="12" t="inlineStr">
         <is>
-          <t>Privacy is not absolute; where paternity is directly in issue and no other evidence can settle it, a DNA test may be ordered. The Civil Court was directed to fix a date for the test.</t>
+          <t>Forced DNA testing is a grave intrusion on privacy and must be lawful, necessary and proportionate, with a nexus to the offence. Paternity was collateral to the charges, so the direction was set aside.</t>
         </is>
       </c>
       <c r="N16" s="12" t="inlineStr">
         <is>
-          <t>Aparna Ajinkya Firodia v. Ajinkya Arun Firodia (2023)</t>
+          <t>Goutam Kundu v. State of West Bengal (1993)</t>
         </is>
       </c>
       <c r="O16" s="12" t="inlineStr">
         <is>
-          <t>https://api.sci.gov.in/supremecourt/2025/50840/50840_2025_8_1502_71638_Judgement_29-May-2026.pdf</t>
+          <t>https://api.sci.gov.in/supremecourt/2017/16058/16058_2017_14_1501_65616_Judgement_10-Nov-2025.pdf</t>
         </is>
       </c>
       <c r="P16" s="12" t="inlineStr">
         <is>
-          <t>Anmol Kumar Sinha</t>
+          <t>Khushi Gurm</t>
         </is>
       </c>
     </row>
@@ -1772,41 +1772,153 @@
       <c r="A17" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="B17" s="12" t="n"/>
-      <c r="C17" s="12" t="n"/>
-      <c r="D17" s="12" t="n"/>
-      <c r="E17" s="12" t="n"/>
-      <c r="F17" s="12" t="n"/>
-      <c r="G17" s="12" t="n"/>
-      <c r="H17" s="12" t="n"/>
-      <c r="I17" s="12" t="n"/>
-      <c r="J17" s="12" t="n"/>
-      <c r="K17" s="12" t="n"/>
-      <c r="L17" s="12" t="n"/>
-      <c r="M17" s="12" t="n"/>
-      <c r="N17" s="12" t="n"/>
-      <c r="O17" s="12" t="n"/>
-      <c r="P17" s="12" t="n"/>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>Harish Rana v. Union of India</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>2026 INSC 222 (M.A. No. 2238 of 2025 in SLP (C) No. 18225 of 2024)</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>11-03-2026</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F17" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="H17" s="12" t="inlineStr">
+        <is>
+          <t>Individual</t>
+        </is>
+      </c>
+      <c r="I17" s="12" t="inlineStr">
+        <is>
+          <t>Allowed</t>
+        </is>
+      </c>
+      <c r="J17" s="12" t="inlineStr">
+        <is>
+          <t>Individual</t>
+        </is>
+      </c>
+      <c r="K17" s="12" t="inlineStr">
+        <is>
+          <t>Art 21 (paras 299–305, 307–312, 324–327)</t>
+        </is>
+      </c>
+      <c r="L17" s="12" t="inlineStr">
+        <is>
+          <t>How passive euthanasia applies to a patient in a permanent vegetative state who cannot consent and left no advance directive.</t>
+        </is>
+      </c>
+      <c r="M17" s="12" t="inlineStr">
+        <is>
+          <t>Clinically assisted nutrition and hydration is medical treatment; applying the best-interest principle through the Common Cause procedure, with family and medical boards deciding for him, the Court permitted its withdrawal and disposed of the application with directions.</t>
+        </is>
+      </c>
+      <c r="N17" s="12" t="inlineStr">
+        <is>
+          <t>Common Cause v. Union of India (2018)</t>
+        </is>
+      </c>
+      <c r="O17" s="12" t="inlineStr">
+        <is>
+          <t>https://api.sci.gov.in/supremecourt/2025/60980/60980_2025_7_1501_69246_Judgement_11-Mar-2026.pdf</t>
+        </is>
+      </c>
+      <c r="P17" s="12" t="inlineStr">
+        <is>
+          <t>Astitva Agrawal</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="40" customHeight="1">
       <c r="A18" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="B18" s="12" t="n"/>
-      <c r="C18" s="12" t="n"/>
-      <c r="D18" s="12" t="n"/>
-      <c r="E18" s="12" t="n"/>
-      <c r="F18" s="12" t="n"/>
-      <c r="G18" s="12" t="n"/>
-      <c r="H18" s="12" t="n"/>
-      <c r="I18" s="12" t="n"/>
-      <c r="J18" s="12" t="n"/>
-      <c r="K18" s="12" t="n"/>
-      <c r="L18" s="12" t="n"/>
-      <c r="M18" s="12" t="n"/>
-      <c r="N18" s="12" t="n"/>
-      <c r="O18" s="12" t="n"/>
-      <c r="P18" s="12" t="n"/>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>Chaturbhuj Pradhan v. Amar Pradhan</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>2026 INSC 600 (arising out of SLP (C) No. 4016 of 2026)</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>29-05-2026</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F18" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>Civil appeal</t>
+        </is>
+      </c>
+      <c r="H18" s="12" t="inlineStr">
+        <is>
+          <t>Individual</t>
+        </is>
+      </c>
+      <c r="I18" s="12" t="inlineStr">
+        <is>
+          <t>Dismissed</t>
+        </is>
+      </c>
+      <c r="J18" s="12" t="inlineStr">
+        <is>
+          <t>Individual</t>
+        </is>
+      </c>
+      <c r="K18" s="12" t="inlineStr">
+        <is>
+          <t>s 112 Evidence Act; Art 21 (paras 5.3–7)</t>
+        </is>
+      </c>
+      <c r="L18" s="12" t="inlineStr">
+        <is>
+          <t>Whether a man could be compelled to take a DNA test in a suit where the plaintiff claims to be his son.</t>
+        </is>
+      </c>
+      <c r="M18" s="12" t="inlineStr">
+        <is>
+          <t>Privacy is not absolute; where paternity is directly in issue and no other evidence can settle it, a DNA test may be ordered. The Civil Court was directed to fix a date for the test.</t>
+        </is>
+      </c>
+      <c r="N18" s="12" t="inlineStr">
+        <is>
+          <t>Ivan Rathinam v. Milan Joseph (2025)</t>
+        </is>
+      </c>
+      <c r="O18" s="12" t="inlineStr">
+        <is>
+          <t>https://api.sci.gov.in/supremecourt/2025/50840/50840_2025_8_1502_71638_Judgement_29-May-2026.pdf</t>
+        </is>
+      </c>
+      <c r="P18" s="12" t="inlineStr">
+        <is>
+          <t>Anmol Kumar Sinha</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="40" customHeight="1">
       <c r="A19" s="11" t="n">
@@ -1949,10 +2061,22 @@
       <c r="P25" s="12" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="5">
+  <dataValidations count="9">
     <dataValidation sqref="E6:E25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Year" error="Enter a year between 2021 and 2026 as a number." type="whole">
       <formula1>2021</formula1>
       <formula2>2026</formula2>
+    </dataValidation>
+    <dataValidation sqref="G6:G25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+      <formula1>=Vocabularies!$A$3:$A$7</formula1>
+    </dataValidation>
+    <dataValidation sqref="H6:H25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+      <formula1>=Vocabularies!$B$3:$B$7</formula1>
+    </dataValidation>
+    <dataValidation sqref="I6:I25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+      <formula1>=Vocabularies!$C$3:$C$6</formula1>
+    </dataValidation>
+    <dataValidation sqref="J6:J25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+      <formula1>=Vocabularies!$D$3:$D$7</formula1>
     </dataValidation>
     <dataValidation sqref="G6:G25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=Vocabularies!$A$3:$A$7</formula1>
